--- a/cypress/fixtures/archivos/tecnicos_rol_no_permitido.xlsx
+++ b/cypress/fixtures/archivos/tecnicos_rol_no_permitido.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9000000813</t>
+          <t>1900000813</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
